--- a/docs/test_report/ethfw_testreport_j721s2.xlsx
+++ b/docs/test_report/ethfw_testreport_j721s2.xlsx
@@ -599,12 +599,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2022-12-09 04:03:29.723864-06:00 CDT</t>
+          <t>2023-02-14 18:39:49.756470-06:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr"/>
@@ -1281,12 +1281,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr"/>
@@ -1376,12 +1376,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
@@ -1469,12 +1469,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr"/>
@@ -1564,12 +1564,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1661,12 +1661,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr"/>
@@ -1755,12 +1755,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr"/>
@@ -1848,12 +1848,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr"/>
@@ -1941,12 +1941,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr"/>
@@ -2034,12 +2034,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr"/>
@@ -2127,12 +2127,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr"/>
@@ -2220,12 +2220,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2052</t>
+          <t>ETHFW-2133</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Plan (j721s2)</t>
+          <t>Enet 8.6 Release Test Plan (j721s2)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2057</t>
+          <t>ETHFW-2138</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>Enet 8.5 Release Test Run (j721s2)</t>
+          <t>Enet 8.6 Release Test Run (j721s2)</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr"/>
